--- a/output/pdf_financials_xlsx/LAS.A.xlsx
+++ b/output/pdf_financials_xlsx/LAS.A.xlsx
@@ -6422,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>1.382</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0</v>
@@ -31544,7 +31544,11 @@
           <t>(304)      4,325            4,021             2,671           (2,975)       (304)            $     Equity                                                                     Hedging reserve</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LAS.A.xlsx
+++ b/output/pdf_financials_xlsx/LAS.A.xlsx
@@ -2354,28 +2354,28 @@
         <v>44.627</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>45.214</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>48.752</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>56.957</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>59.505</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>59.513</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>63.267</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>80.527</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>111.649</v>
       </c>
     </row>
     <row r="29">
@@ -7000,28 +7000,28 @@
         <v>44.627</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>45.214</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>48.752</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>56.957</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>59.505</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>59.513</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>63.267</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>80.527</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>111.649</v>
       </c>
     </row>
     <row r="101">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>2.255</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -8609,10 +8609,10 @@
         <v>0</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0</v>
+        <v>-0.776</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>0</v>
+        <v>-1.008</v>
       </c>
       <c r="L126" s="3" t="n">
         <v>0</v>
@@ -41904,7 +41904,11 @@
           <t>Depreciation of right-of-use assets and property, plant and equipment and amortization of intangible assets 7</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -45033,7 +45037,11 @@
           <t>Depreciation of property, plant and equipment and amortization of intangible assets 8</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -46490,7 +46498,11 @@
           <t>Depreciation of property, plant and equipment and amortization of intangible assets 8</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -48534,7 +48546,11 @@
           <t>Depreciation of property, plant and equipment and amortization of intangible assets 7</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -50099,7 +50115,11 @@
           <t>Depreciation of property, plant and equipment and amortization of intangible assets 9</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -51643,7 +51663,11 @@
           <t>Dividends paid to the non-controlling interest 23</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E432" t="inlineStr">
         <is>
           <t>-</t>
@@ -52324,7 +52348,11 @@
           <t>Dividends paid to the non-controlling interest 22</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -53215,7 +53243,11 @@
           <t>Dividends paid to the non-controlling interest</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -58561,7 +58593,11 @@
           <t>Proceeds from the disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
           <t>-</t>
